--- a/artfynd/A 59552-2025 artfynd.xlsx
+++ b/artfynd/A 59552-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4214947</v>
+        <v>110927506</v>
       </c>
       <c r="B2" t="n">
-        <v>95518</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>350 m ONO om Sannetorpet, Ormestad, Boh</t>
+          <t>Bokenäset, Ormestad, norr om Valefjälls norra topp, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>301371.1405048387</v>
+        <v>301357</v>
       </c>
       <c r="R2" t="n">
-        <v>6473555.756865029</v>
+        <v>6473640</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1999-07-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1999-07-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,71 +758,80 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Hällmarksblandskog</t>
+        </is>
+      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>granskog</t>
+          <t>Äldre naturskogsliknande senvuxen skog; grandoinerat</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Föreningen Bohusläns Flora</t>
+          <t>Mats Lindqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Föreningen Bohusläns Flora</t>
+          <t>Mats Lindqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>90954503</v>
+        <v>110927461</v>
       </c>
       <c r="B3" t="n">
-        <v>97522</v>
+        <v>75428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Cirka 350 m ONO om Sannetorpet, mellan de två höjderna på Valefjäll, Boh</t>
+          <t>Bokenäset, Ormestad, norr om Valefjälls norra topp, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>301376</v>
+        <v>301357</v>
       </c>
       <c r="R3" t="n">
-        <v>6473561</v>
+        <v>6473640</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,17 +855,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1999-07-14</t>
+          <t>2023-07-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1999-07-14</t>
+          <t>2023-07-17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Bohusläns flora - 2011.</t>
+          <t>Med Lecanactis abietina</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,18 +874,39 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Hällmarksblandskog</t>
+        </is>
+      </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Sänka</t>
+          <t>Äldre naturskogsliknande senvuxen skog; grandoinerat</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Evastina Blomgren</t>
+          <t>Mats Lindqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -895,23 +914,14 @@
           <t>Mats Lindqvist</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Bohusläns Flora 2011</t>
-        </is>
-      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110927461</v>
+        <v>4214947</v>
       </c>
       <c r="B4" t="n">
-        <v>73634</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,40 +929,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bokenäset, Ormestad, norr om Valefjälls norra topp, Boh</t>
+          <t>350 m ONO om Sannetorpet, Ormestad, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>301356.9934798228</v>
+        <v>301371</v>
       </c>
       <c r="R4" t="n">
-        <v>6473640.571394845</v>
+        <v>6473556</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,27 +983,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-07-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Med Lecanactis abietina</t>
+          <t>1999-07-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,59 +997,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Hällmarksblandskog</t>
-        </is>
-      </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Äldre naturskogsliknande senvuxen skog; grandoinerat</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>granskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mats Lindqvist</t>
+          <t>Föreningen Bohusläns Flora</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mats Lindqvist</t>
+          <t>Föreningen Bohusläns Flora</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110927506</v>
+        <v>90954503</v>
       </c>
       <c r="B5" t="n">
-        <v>94851</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1065,41 +1031,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bokenäset, Ormestad, norr om Valefjälls norra topp, Boh</t>
+          <t>Cirka 350 m ONO om Sannetorpet, mellan de två höjderna på Valefjäll, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>301356.9934798228</v>
+        <v>301376</v>
       </c>
       <c r="R5" t="n">
-        <v>6473640.571394845</v>
+        <v>6473561</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,22 +1085,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-07-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-07-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bohusläns flora - 2011.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,32 +1104,30 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Hällmarksblandskog</t>
-        </is>
-      </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Äldre naturskogsliknande senvuxen skog; grandoinerat</t>
+          <t>Sänka</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Evastina Blomgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
           <t>Mats Lindqvist</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Mats Lindqvist</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Bohusläns Flora 2011</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59552-2025 artfynd.xlsx
+++ b/artfynd/A 59552-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110927506</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110927461</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4214947</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,8 +1148,19 @@
           <t>Bohusläns Flora 2011</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90954503</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>